--- a/MSME/Test upload format/MSME_Continuity - 3.xlsx
+++ b/MSME/Test upload format/MSME_Continuity - 3.xlsx
@@ -8,7 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
   <si>
     <t>CGPAN</t>
   </si>
@@ -53,67 +57,118 @@
     <t>NPAInterestAmount</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357196</t>
+    <t>CGMSMGEN2210202600357241</t>
+  </si>
+  <si>
+    <t>Aloan04</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2210202600357242</t>
   </si>
   <si>
     <t>Aloan05</t>
   </si>
   <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2209202600357197</t>
+    <t>CGMSMGEN2210202600357243</t>
   </si>
   <si>
     <t>Aloan06</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357198</t>
+    <t>CGMSMGEN2210202600357244</t>
   </si>
   <si>
     <t>Aloan07</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357202</t>
+    <t>CGMSMGEN2210202600357248</t>
   </si>
   <si>
     <t>Aloan11</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357203</t>
+    <t>CGMSMGEN2210202600357249</t>
   </si>
   <si>
     <t>Aloan12</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357208</t>
+    <t>CGMSMGEN2210202600357253</t>
+  </si>
+  <si>
+    <t>Aloan16</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2210202600357254</t>
   </si>
   <si>
     <t>Aloan17</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357209</t>
+    <t>CGMSMGEN2210202600357255</t>
   </si>
   <si>
     <t>Aloan18</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357210</t>
+    <t>CGMSMGEN2210202600357256</t>
   </si>
   <si>
     <t>Aloan19</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357214</t>
+    <t>CGMSMGEN2210202600357257</t>
+  </si>
+  <si>
+    <t>Aloan20</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2210202600357258</t>
+  </si>
+  <si>
+    <t>Aloan21</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2210202600357259</t>
+  </si>
+  <si>
+    <t>Aloan22</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2210202600357260</t>
   </si>
   <si>
     <t>Aloan23</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357215</t>
+    <t>CGMSMGEN2210202600357261</t>
   </si>
   <si>
     <t>Aloan24</t>
+  </si>
+  <si>
+    <t>NPA</t>
+  </si>
+  <si>
+    <t>27-02-2029</t>
+  </si>
+  <si>
+    <t>40000000</t>
+  </si>
+  <si>
+    <t>100000000</t>
+  </si>
+  <si>
+    <t>10000000</t>
+  </si>
+  <si>
+    <t>300000000</t>
+  </si>
+  <si>
+    <t>460000000</t>
   </si>
 </sst>
 </file>
@@ -126,13 +181,25 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -145,12 +212,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -306,7 +367,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,6 +376,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -500,7 +567,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -510,19 +577,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4"/>
-      </left>
       <right/>
       <top style="thin">
         <color theme="4"/>
@@ -633,70 +687,67 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -711,77 +762,83 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -790,18 +847,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1064,222 +1121,545 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="33.4285714285714" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.7809523809524" style="3" customWidth="1"/>
-    <col min="3" max="3" width="34.2857142857143" style="3" customWidth="1"/>
-    <col min="4" max="4" width="21.2857142857143" style="4" customWidth="1"/>
-    <col min="5" max="5" width="25.7142857142857" style="3" customWidth="1"/>
-    <col min="6" max="6" width="30.2857142857143" style="4" customWidth="1"/>
-    <col min="7" max="7" width="38" style="3" customWidth="1"/>
-    <col min="8" max="8" width="28.1428571428571" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="12.6666666666667" style="3"/>
+    <col min="1" max="1" width="33.4285714285714" style="6" customWidth="1"/>
+    <col min="2" max="2" width="22.7809523809524" style="6" customWidth="1"/>
+    <col min="3" max="3" width="34.2857142857143" style="6" customWidth="1"/>
+    <col min="4" max="4" width="21.2857142857143" style="8" customWidth="1"/>
+    <col min="5" max="5" width="25.7142857142857" style="6" customWidth="1"/>
+    <col min="6" max="6" width="30.2857142857143" style="8" customWidth="1"/>
+    <col min="7" max="7" width="38" style="6" customWidth="1"/>
+    <col min="8" max="8" width="28.1428571428571" style="6" customWidth="1"/>
+    <col min="9" max="16384" width="12.6666666666667" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" s="4" customFormat="1" spans="1:8">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="15" spans="1:8">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="5" customFormat="1" ht="15" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6">
-        <v>600000000</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="C2" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="D2" s="2">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:8">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6">
-        <v>500000000</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="2">
+        <v>600000000</v>
+      </c>
+      <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="15" spans="1:8">
-      <c r="A4" s="6" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6">
-        <v>200000000</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="15" spans="1:8">
-      <c r="A5" s="6" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="6">
-        <v>180000000</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="2">
+        <v>200000000</v>
+      </c>
+      <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" ht="15" spans="1:8">
-      <c r="A6" s="6" t="s">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6">
-        <v>20000000</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="2">
+        <v>180000000</v>
+      </c>
+      <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" ht="15" spans="1:8">
-      <c r="A7" s="6" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6">
-        <v>600000000</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" ht="15" spans="1:8">
-      <c r="A8" s="6" t="s">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="2">
         <v>500000000</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" ht="15" spans="1:8">
-      <c r="A9" s="6" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="6">
-        <v>200000000</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="2">
+        <v>600000000</v>
+      </c>
+      <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" ht="15" spans="1:8">
-      <c r="A10" s="6" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6">
-        <v>180000000</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" ht="15" spans="1:8">
-      <c r="A11" s="6" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="6">
-        <v>20000000</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="2">
+        <v>200000000</v>
+      </c>
+      <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" s="7" customFormat="1" ht="15" spans="1:8">
+      <c r="A12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" s="7" customFormat="1" ht="15" spans="1:8">
+      <c r="A13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="11">
+        <v>150000000</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" s="7" customFormat="1" ht="15" spans="1:8">
+      <c r="A14" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="D14" s="11">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2">
+        <v>180000000</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" s="6" customFormat="1" ht="15" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H5" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75" outlineLevelRow="6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" ht="15" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="D1" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2">
+        <v>200000000</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2">
+        <v>180000000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2">
+        <v>600000000</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>